--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikas\IdeaProjects\PlaywrightAutomation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D58F878-FF92-46C4-83A9-6A578A326042}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F813EC3-041F-4278-83B1-5676246063C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{29B1413F-B7ED-476E-B613-83BCCD37154B}"/>
   </bookViews>
@@ -30,10 +30,10 @@
     <t>Email</t>
   </si>
   <si>
-    <t>test4@zohomail.in</t>
+    <t>test7@zohomail.in</t>
   </si>
   <si>
-    <t>test5@zohomail.in</t>
+    <t>test8@zohomail.in</t>
   </si>
 </sst>
 </file>

--- a/src/test/resources/TestData.xlsx
+++ b/src/test/resources/TestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikas\IdeaProjects\PlaywrightAutomation\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F813EC3-041F-4278-83B1-5676246063C4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134D8236-636B-494D-8284-F53D00ED4DFB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" xr2:uid="{29B1413F-B7ED-476E-B613-83BCCD37154B}"/>
   </bookViews>
@@ -30,10 +30,10 @@
     <t>Email</t>
   </si>
   <si>
-    <t>test7@zohomail.in</t>
+    <t>test10@zohomail.in</t>
   </si>
   <si>
-    <t>test8@zohomail.in</t>
+    <t>test11@zohomail.in</t>
   </si>
 </sst>
 </file>
